--- a/output/rf_dgp1_output.xlsx
+++ b/output/rf_dgp1_output.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5cac48941448979/Bureaublad/msc_thesis/thesis_code/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_42CED800BC172A856E6EAC99441620EDE9E2BF29" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9E9E794-5CE9-48FC-8569-6741C70BC550}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_42CED800506763D5321EB882DCF42CEDE9E2BF35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{567836EC-D236-481F-85EB-366A2290A0E1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,52 +378,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.28799999999999998</v>
+        <v>0.20499999999999999</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.29499999999999998</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.26600000000000001</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.28599999999999998</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.25</v>
+        <v>0.23300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.25600000000000001</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.27600000000000002</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.29399999999999998</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.253</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.28199999999999997</v>
+        <v>0.21099999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -432,7 +432,7 @@
       </c>
       <c r="B12">
         <f>AVERAGE(A1:A10)</f>
-        <v>0.27460000000000001</v>
+        <v>0.21129999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -441,7 +441,7 @@
       </c>
       <c r="B13">
         <f>_xlfn.STDEV.S(A1:A10)</f>
-        <v>1.7160678567262094E-2</v>
+        <v>1.5085312945599333E-2</v>
       </c>
     </row>
   </sheetData>
@@ -457,52 +457,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.38685633600000002</v>
+        <v>0.30185479999999998</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.40737017599999997</v>
+        <v>0.25304096799999998</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.372719984</v>
+        <v>0.28031936800000001</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.40282391200000001</v>
+        <v>0.33229365599999999</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.34762423199999998</v>
+        <v>0.31909206400000001</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.36578799200000001</v>
+        <v>0.31564442399999998</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.40004150399999999</v>
+        <v>0.30046165600000002</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.39751982400000002</v>
+        <v>0.30476375999999999</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.35812744800000001</v>
+        <v>0.30243339200000002</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.39948107199999999</v>
+        <v>0.28849992000000002</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -511,7 +511,7 @@
       </c>
       <c r="B12">
         <f>AVERAGE(A1:A10)</f>
-        <v>0.38383524799999996</v>
+        <v>0.29984040080000007</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -520,7 +520,7 @@
       </c>
       <c r="B13">
         <f>_xlfn.STDEV.S(A1:A10)</f>
-        <v>2.1186139429042856E-2</v>
+        <v>2.213312857947523E-2</v>
       </c>
     </row>
   </sheetData>
